--- a/data/semesters/sem2/cohorts.xlsx
+++ b/data/semesters/sem2/cohorts.xlsx
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
